--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
   <si>
     <t>Event_Name</t>
   </si>
@@ -120,6 +120,33 @@
   </si>
   <si>
     <t>Swachhta Hi Seva Agra</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Ghaziabad</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Kota</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Udaipur</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Varanasi</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Faridabad</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Kanpur</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Nagpur</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Dehradun</t>
+  </si>
+  <si>
+    <t>Swachhta Hi Seva Prayagraj</t>
   </si>
 </sst>
 </file>
@@ -164,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A53"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -347,6 +374,91 @@
         <v>35</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="45">
   <si>
     <t>Event_Name</t>
   </si>
@@ -191,7 +191,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -459,6 +459,11 @@
         <v>44</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Event_Name</t>
   </si>
@@ -159,6 +159,12 @@
   </si>
   <si>
     <t>Prayagraj Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Indore Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Dehradun Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -203,7 +209,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A59"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -501,6 +507,21 @@
         <v>48</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="52">
   <si>
     <t>Event_Name</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Dehradun Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Udaipur Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -209,7 +212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A64"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -522,6 +525,16 @@
         <v>50</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
   <si>
     <t>Event_Name</t>
   </si>
@@ -171,6 +171,9 @@
   </si>
   <si>
     <t>Faridabad Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Pune Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -215,7 +218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A65"/>
+  <dimension ref="A1:A66"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -543,6 +546,11 @@
         <v>52</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="56">
   <si>
     <t>Event_Name</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>Pune Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Ranchi Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Nagpur Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -218,7 +224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A66"/>
+  <dimension ref="A1:A69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -551,6 +557,21 @@
         <v>53</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
   <si>
     <t>Event_Name</t>
   </si>
@@ -183,6 +183,12 @@
   </si>
   <si>
     <t>Noida Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Jaipur Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Patna Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -227,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A70"/>
+  <dimension ref="A1:A73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -580,6 +586,21 @@
         <v>56</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
   <si>
     <t>Event_Name</t>
   </si>
@@ -233,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A73"/>
+  <dimension ref="A1:A74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -601,6 +601,11 @@
         <v>58</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
   <si>
     <t>Event_Name</t>
   </si>
@@ -233,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A74"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -606,6 +606,11 @@
         <v>49</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
   <si>
     <t>Event_Name</t>
   </si>
@@ -233,7 +233,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A76"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -611,6 +611,11 @@
         <v>50</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
   <si>
     <t>Event_Name</t>
   </si>
@@ -189,6 +189,9 @@
   </si>
   <si>
     <t>Patna Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Kota Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -233,7 +236,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A76"/>
+  <dimension ref="A1:A77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -616,6 +619,11 @@
         <v>52</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t>Event_Name</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>Kota Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Nashik Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -236,7 +239,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A77"/>
+  <dimension ref="A1:A78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -624,6 +627,11 @@
         <v>59</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
   <si>
     <t>Event_Name</t>
   </si>
@@ -195,6 +195,12 @@
   </si>
   <si>
     <t>Nashik Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Agra Swachhta Hi Seva</t>
+  </si>
+  <si>
+    <t>Meerut Swachhta Hi Seva</t>
   </si>
 </sst>
 </file>
@@ -239,7 +245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A78"/>
+  <dimension ref="A1:A81"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -632,6 +638,21 @@
         <v>60</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
   <si>
     <t>Event_Name</t>
   </si>
@@ -245,7 +245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A81"/>
+  <dimension ref="A1:A82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -653,6 +653,11 @@
         <v>48</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/resources/Event_Name.xlsx
+++ b/resources/Event_Name.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
   <si>
     <t>Event_Name</t>
   </si>
@@ -245,7 +245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A82"/>
+  <dimension ref="A1:A83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,11 @@
         <v>48</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
